--- a/Result/profitability/8927.xlsx
+++ b/Result/profitability/8927.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09625000000000003</v>
+        <v>0.11375</v>
       </c>
       <c r="N2" t="n">
-        <v>17.2075</v>
+        <v>16.11875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08375000000000003</v>
+        <v>0.1562500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>15.40375</v>
+        <v>15.5775</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09375000000000003</v>
+        <v>0.14375</v>
       </c>
       <c r="N4" t="n">
-        <v>14.60125</v>
+        <v>14.61625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07125000000000002</v>
+        <v>0.1225</v>
       </c>
       <c r="N5" t="n">
-        <v>13.87125</v>
+        <v>13.67125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.16</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08750000000000004</v>
+        <v>0.135</v>
       </c>
       <c r="N6" t="n">
-        <v>13.515</v>
+        <v>13.15875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.10125</v>
+        <v>0.1275</v>
       </c>
       <c r="N7" t="n">
-        <v>12.62875</v>
+        <v>11.87375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08750000000000004</v>
+        <v>0.12</v>
       </c>
       <c r="N8" t="n">
-        <v>11.12125</v>
+        <v>11.05125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07750000000000003</v>
+        <v>0.07750000000000004</v>
       </c>
       <c r="N10" t="n">
         <v>10.31125</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8927</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4273</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3603</v>
+      </c>
+      <c r="E75" t="n">
+        <v>670</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>314</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>77</v>
+      </c>
+      <c r="J75" t="n">
+        <v>391</v>
+      </c>
+      <c r="K75" t="n">
+        <v>185</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.96125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.444444444444445</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.5599999999999987</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03448275862068961</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.600000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09259259259259267</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
